--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -413,186 +413,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>lob_name</t>
+          <t>stage</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>source_weight</t>
+          <t>severity</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>target_weight</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>line_level_ratio</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>projected_contribution</t>
+          <t>multiplier</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Property</t>
+          <t>raw donor</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.215753</v>
+        <v>0.030697</v>
       </c>
       <c r="C2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.030697</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.010744</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Casualty</t>
+          <t>after size</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.302511</v>
+        <v>0.011129</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.030697</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.009209</v>
+        <v>0.362544</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>after concentration (adjusted)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.010919</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Motor</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.042237</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.030697</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Aviation</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.026256</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.030697</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Reinsurance — Property</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Professional Lines</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Aggregate</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.413242</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.030697</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
+        <v>0.9811</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.011129</v>
+        <v>0.009686</v>
       </c>
       <c r="C3" t="n">
-        <v>0.362544</v>
+        <v>0.315536</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.010919</v>
+        <v>0.009545</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9811</v>
+        <v>0.985453</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.009686</v>
+        <v>0.009483999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.315536</v>
+        <v>0.308944</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009545</v>
+        <v>0.009353</v>
       </c>
       <c r="C4" t="n">
-        <v>0.985453</v>
+        <v>0.98625</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.009483999999999999</v>
+        <v>0.009759</v>
       </c>
       <c r="C3" t="n">
-        <v>0.308944</v>
+        <v>0.317932</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009353</v>
+        <v>0.009627999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.98625</v>
+        <v>0.986514</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-2/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.009759</v>
+        <v>0.009726</v>
       </c>
       <c r="C3" t="n">
-        <v>0.317932</v>
+        <v>0.316828</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009627999999999999</v>
+        <v>0.009596</v>
       </c>
       <c r="C4" t="n">
-        <v>0.986514</v>
+        <v>0.986716</v>
       </c>
     </row>
   </sheetData>
